--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -2283,7 +2283,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -2297,8 +2297,14 @@
       <c r="I39" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J39" s="12" t="n"/>
-      <c r="K39" s="13" t="n"/>
+      <c r="J39" s="12" t="n">
+        <v>46224</v>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Completed via PR #12 (SMS ingestion endpoint, MessageFeature model, API contract docs/api/sms.md).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -2455,7 +2461,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -2469,8 +2475,14 @@
       <c r="I43" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="13" t="n"/>
+      <c r="J43" s="12" t="n">
+        <v>46224</v>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Completed via PR #12 (SMS ingestion endpoint, MessageFeature model, API contract docs/api/sms.md).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -2500,7 +2512,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -2514,8 +2526,14 @@
       <c r="I44" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="13" t="n"/>
+      <c r="J44" s="12" t="n">
+        <v>46224</v>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Completed via PR #12 (SMS ingestion endpoint, MessageFeature model, API contract docs/api/sms.md).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -2577,8 +2577,14 @@
       <c r="I45" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J45" s="12" t="n"/>
-      <c r="K45" s="13" t="n"/>
+      <c r="J45" s="12" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Completed Sprint 2 deliverable; awaiting labeled dataset for training.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
@@ -2637,7 +2643,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Softmax classification head (Likely Smishing / Suspicious / Unknown)</t>
+          <t>Softmax classification head (Ham / Spam / Scam)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -2657,7 +2663,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -2671,8 +2677,14 @@
       <c r="I47" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J47" s="12" t="n"/>
-      <c r="K47" s="13" t="n"/>
+      <c r="J47" s="12" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Completed Sprint 2 deliverable; awaiting labeled dataset for training.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
@@ -2702,7 +2714,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -2716,8 +2728,14 @@
       <c r="I48" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J48" s="12" t="n"/>
-      <c r="K48" s="13" t="n"/>
+      <c r="J48" s="12" t="n">
+        <v>46222</v>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Completed Sprint 2 deliverable; awaiting labeled dataset for training.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -169,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,6 +238,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,7 +678,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="n">
-        <v>46223</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="3">
@@ -696,7 +706,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="38.25" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -1373,7 +1382,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Carryover → S2</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -1424,7 +1433,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Carryover → S2</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -2070,7 +2079,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -2084,7 +2093,9 @@
       <c r="I34" s="24" t="n">
         <v>46240</v>
       </c>
-      <c r="J34" s="6" t="n"/>
+      <c r="J34" s="27" t="n">
+        <v>46241</v>
+      </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">3-week sprint per Agile Model </t>
@@ -2115,7 +2126,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -2129,7 +2140,9 @@
       <c r="I35" s="25" t="n">
         <v>46240</v>
       </c>
-      <c r="J35" s="9" t="n"/>
+      <c r="J35" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K35" s="10" t="n"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
@@ -2156,7 +2169,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2170,7 +2183,9 @@
       <c r="I36" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J36" s="12" t="n"/>
+      <c r="J36" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K36" s="13" t="n"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
@@ -2197,7 +2212,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -2211,7 +2226,9 @@
       <c r="I37" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J37" s="12" t="n"/>
+      <c r="J37" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K37" s="13" t="n"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
@@ -2238,7 +2255,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -2252,7 +2269,9 @@
       <c r="I38" s="25" t="n">
         <v>46240</v>
       </c>
-      <c r="J38" s="9" t="n"/>
+      <c r="J38" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K38" s="10" t="n"/>
     </row>
     <row r="39">
@@ -2334,7 +2353,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -2348,7 +2367,9 @@
       <c r="I40" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J40" s="12" t="n"/>
+      <c r="J40" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -2375,7 +2396,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -2389,7 +2410,9 @@
       <c r="I41" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J41" s="12" t="n"/>
+      <c r="J41" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K41" s="13" t="n"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
@@ -2416,7 +2439,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -2430,7 +2453,9 @@
       <c r="I42" s="25" t="n">
         <v>46240</v>
       </c>
-      <c r="J42" s="9" t="n"/>
+      <c r="J42" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K42" s="10" t="n"/>
     </row>
     <row r="43">
@@ -2614,7 +2639,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -2628,7 +2653,9 @@
       <c r="I46" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J46" s="12" t="n"/>
+      <c r="J46" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
           <t>Combined 4 Kaggle sources</t>
@@ -2986,7 +3013,7 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -3000,7 +3027,9 @@
       <c r="I54" s="25" t="n">
         <v>46240</v>
       </c>
-      <c r="J54" s="9" t="n"/>
+      <c r="J54" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K54" s="10" t="n"/>
     </row>
     <row r="55">
@@ -3031,7 +3060,7 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -3045,7 +3074,9 @@
       <c r="I55" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J55" s="12" t="n"/>
+      <c r="J55" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K55" s="13" t="n"/>
     </row>
     <row r="56">
@@ -3076,7 +3107,7 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -3090,7 +3121,9 @@
       <c r="I56" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J56" s="12" t="n"/>
+      <c r="J56" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K56" s="13" t="n"/>
     </row>
     <row r="57">
@@ -3121,7 +3154,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -3135,7 +3168,9 @@
       <c r="I57" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J57" s="12" t="n"/>
+      <c r="J57" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K57" s="13" t="n"/>
     </row>
     <row r="58" ht="25.5" customHeight="1">
@@ -3162,7 +3197,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -3176,7 +3211,9 @@
       <c r="I58" s="25" t="n">
         <v>46240</v>
       </c>
-      <c r="J58" s="9" t="n"/>
+      <c r="J58" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K58" s="10" t="n"/>
     </row>
     <row r="59">
@@ -3207,7 +3244,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -3221,7 +3258,9 @@
       <c r="I59" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J59" s="12" t="n"/>
+      <c r="J59" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K59" s="13" t="n"/>
     </row>
     <row r="60">
@@ -3248,7 +3287,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -3262,7 +3301,9 @@
       <c r="I60" s="26" t="n">
         <v>46240</v>
       </c>
-      <c r="J60" s="12" t="n"/>
+      <c r="J60" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K60" s="13" t="n"/>
     </row>
     <row r="61" ht="25.5" customHeight="1">
@@ -3289,7 +3330,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -3303,7 +3344,9 @@
       <c r="I61" s="24" t="n">
         <v>46261</v>
       </c>
-      <c r="J61" s="6" t="n"/>
+      <c r="J61" s="27" t="n">
+        <v>46241</v>
+      </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">3-week sprint per Agile Model </t>
@@ -3334,7 +3377,7 @@
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -3348,7 +3391,9 @@
       <c r="I62" s="25" t="n">
         <v>46261</v>
       </c>
-      <c r="J62" s="9" t="n"/>
+      <c r="J62" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K62" s="10" t="n"/>
     </row>
     <row r="63">
@@ -3375,7 +3420,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -3389,7 +3434,9 @@
       <c r="I63" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J63" s="12" t="n"/>
+      <c r="J63" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K63" s="13" t="n"/>
     </row>
     <row r="64" ht="25.5" customHeight="1">
@@ -3416,7 +3463,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -3430,7 +3477,9 @@
       <c r="I64" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J64" s="12" t="n"/>
+      <c r="J64" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K64" s="13" t="n"/>
     </row>
     <row r="65" ht="25.5" customHeight="1">
@@ -3457,7 +3506,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3471,7 +3520,9 @@
       <c r="I65" s="25" t="n">
         <v>46261</v>
       </c>
-      <c r="J65" s="9" t="n"/>
+      <c r="J65" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K65" s="10" t="n"/>
     </row>
     <row r="66">
@@ -3502,7 +3553,7 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -3516,7 +3567,9 @@
       <c r="I66" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J66" s="12" t="n"/>
+      <c r="J66" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K66" s="13" t="n"/>
     </row>
     <row r="67">
@@ -3543,7 +3596,7 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -3557,7 +3610,9 @@
       <c r="I67" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J67" s="12" t="n"/>
+      <c r="J67" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K67" s="13" t="n"/>
     </row>
     <row r="68">
@@ -3584,7 +3639,7 @@
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -3598,7 +3653,9 @@
       <c r="I68" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J68" s="12" t="n"/>
+      <c r="J68" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K68" s="13" t="n"/>
     </row>
     <row r="69" ht="25.5" customHeight="1">
@@ -3625,7 +3682,7 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -3639,7 +3696,9 @@
       <c r="I69" s="25" t="n">
         <v>46261</v>
       </c>
-      <c r="J69" s="9" t="n"/>
+      <c r="J69" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K69" s="10" t="n"/>
     </row>
     <row r="70" ht="25.5" customHeight="1">
@@ -3670,7 +3729,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -3684,7 +3743,9 @@
       <c r="I70" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J70" s="12" t="n"/>
+      <c r="J70" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K70" s="13" t="n"/>
     </row>
     <row r="71">
@@ -3715,7 +3776,7 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -3729,7 +3790,9 @@
       <c r="I71" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J71" s="12" t="n"/>
+      <c r="J71" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K71" s="13" t="n"/>
     </row>
     <row r="72">
@@ -3760,7 +3823,7 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -3774,7 +3837,9 @@
       <c r="I72" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J72" s="12" t="n"/>
+      <c r="J72" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K72" s="13" t="n"/>
     </row>
     <row r="73" ht="25.5" customHeight="1">
@@ -3805,7 +3870,7 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -3819,7 +3884,9 @@
       <c r="I73" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J73" s="12" t="n"/>
+      <c r="J73" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K73" s="13" t="n"/>
     </row>
     <row r="74">
@@ -3850,7 +3917,7 @@
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -3864,7 +3931,9 @@
       <c r="I74" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J74" s="12" t="n"/>
+      <c r="J74" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K74" s="13" t="n"/>
     </row>
     <row r="75">
@@ -3895,7 +3964,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -3909,7 +3978,9 @@
       <c r="I75" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J75" s="12" t="n"/>
+      <c r="J75" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K75" s="13" t="n"/>
     </row>
     <row r="76">
@@ -3940,7 +4011,7 @@
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -3954,7 +4025,9 @@
       <c r="I76" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J76" s="12" t="n"/>
+      <c r="J76" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K76" s="13" t="n"/>
     </row>
     <row r="77">
@@ -3985,7 +4058,7 @@
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -3999,7 +4072,9 @@
       <c r="I77" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J77" s="12" t="n"/>
+      <c r="J77" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K77" s="13" t="n"/>
     </row>
     <row r="78">
@@ -4030,7 +4105,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -4044,7 +4119,9 @@
       <c r="I78" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J78" s="12" t="n"/>
+      <c r="J78" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K78" s="13" t="n"/>
     </row>
     <row r="79" ht="25.5" customHeight="1">
@@ -4071,7 +4148,7 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -4085,7 +4162,9 @@
       <c r="I79" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J79" s="12" t="n"/>
+      <c r="J79" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K79" s="13" t="n"/>
     </row>
     <row r="80">
@@ -4116,7 +4195,7 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -4130,7 +4209,9 @@
       <c r="I80" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J80" s="12" t="n"/>
+      <c r="J80" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K80" s="13" t="n"/>
     </row>
     <row r="81" ht="25.5" customHeight="1">
@@ -4161,7 +4242,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -4175,7 +4256,9 @@
       <c r="I81" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J81" s="12" t="n"/>
+      <c r="J81" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K81" s="13" t="n"/>
     </row>
     <row r="82" ht="25.5" customHeight="1">
@@ -4206,7 +4289,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -4220,7 +4303,9 @@
       <c r="I82" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J82" s="12" t="n"/>
+      <c r="J82" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K82" s="13" t="n"/>
     </row>
     <row r="83" ht="25.5" customHeight="1">
@@ -4247,7 +4332,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
@@ -4261,7 +4346,9 @@
       <c r="I83" s="25" t="n">
         <v>46261</v>
       </c>
-      <c r="J83" s="9" t="n"/>
+      <c r="J83" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K83" s="10" t="n"/>
     </row>
     <row r="84">
@@ -4292,7 +4379,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -4306,7 +4393,9 @@
       <c r="I84" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J84" s="12" t="n"/>
+      <c r="J84" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K84" s="13" t="n"/>
     </row>
     <row r="85">
@@ -4337,7 +4426,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -4351,7 +4440,9 @@
       <c r="I85" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J85" s="12" t="n"/>
+      <c r="J85" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K85" s="13" t="n"/>
     </row>
     <row r="86" ht="25.5" customHeight="1">
@@ -4382,7 +4473,7 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -4396,7 +4487,9 @@
       <c r="I86" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J86" s="12" t="n"/>
+      <c r="J86" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K86" s="13" t="n"/>
     </row>
     <row r="87" ht="25.5" customHeight="1">
@@ -4423,7 +4516,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
@@ -4437,7 +4530,9 @@
       <c r="I87" s="25" t="n">
         <v>46261</v>
       </c>
-      <c r="J87" s="9" t="n"/>
+      <c r="J87" s="28" t="n">
+        <v>46241</v>
+      </c>
       <c r="K87" s="10" t="n"/>
     </row>
     <row r="88" ht="25.5" customHeight="1">
@@ -4468,7 +4563,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -4482,7 +4577,9 @@
       <c r="I88" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J88" s="12" t="n"/>
+      <c r="J88" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K88" s="13" t="n"/>
     </row>
     <row r="89">
@@ -4509,7 +4606,7 @@
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -4523,7 +4620,9 @@
       <c r="I89" s="26" t="n">
         <v>46261</v>
       </c>
-      <c r="J89" s="12" t="n"/>
+      <c r="J89" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K89" s="13" t="n"/>
     </row>
     <row r="90" ht="25.5" customHeight="1">
@@ -4550,7 +4649,7 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4595,7 +4694,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4677,7 +4776,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -4691,7 +4790,9 @@
       <c r="I93" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J93" s="12" t="n"/>
+      <c r="J93" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K93" s="13" t="n"/>
     </row>
     <row r="94" ht="25.5" customHeight="1">
@@ -4718,7 +4819,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -4808,7 +4909,7 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -4822,7 +4923,9 @@
       <c r="I96" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J96" s="12" t="n"/>
+      <c r="J96" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K96" s="13" t="n"/>
     </row>
     <row r="97">
@@ -4853,7 +4956,7 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -4867,7 +4970,9 @@
       <c r="I97" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J97" s="12" t="n"/>
+      <c r="J97" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K97" s="13" t="n"/>
     </row>
     <row r="98" ht="25.5" customHeight="1">
@@ -4894,7 +4999,7 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
@@ -5164,7 +5269,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -5178,7 +5283,9 @@
       <c r="I104" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J104" s="12" t="n"/>
+      <c r="J104" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K104" s="13" t="n"/>
     </row>
     <row r="105">
@@ -5209,7 +5316,7 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -5223,7 +5330,9 @@
       <c r="I105" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J105" s="12" t="n"/>
+      <c r="J105" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K105" s="13" t="n"/>
     </row>
     <row r="106">
@@ -5254,7 +5363,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -5295,7 +5404,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -5309,7 +5418,9 @@
       <c r="I107" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J107" s="12" t="n"/>
+      <c r="J107" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
           <t>Independent pipeline</t>
@@ -5344,7 +5455,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -5389,7 +5500,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -5434,7 +5545,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -5479,7 +5590,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -5493,7 +5604,9 @@
       <c r="I111" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J111" s="12" t="n"/>
+      <c r="J111" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K111" s="13" t="n"/>
     </row>
     <row r="112" ht="25.5" customHeight="1">
@@ -5524,7 +5637,7 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -5538,7 +5651,9 @@
       <c r="I112" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J112" s="12" t="n"/>
+      <c r="J112" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K112" s="13" t="n"/>
     </row>
     <row r="113" ht="25.5" customHeight="1">
@@ -5569,7 +5684,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -5583,7 +5698,9 @@
       <c r="I113" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J113" s="12" t="n"/>
+      <c r="J113" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K113" s="13" t="n"/>
     </row>
     <row r="114" ht="25.5" customHeight="1">
@@ -5610,7 +5727,7 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
@@ -5700,7 +5817,7 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -5714,7 +5831,9 @@
       <c r="I116" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J116" s="12" t="n"/>
+      <c r="J116" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K116" s="13" t="n"/>
     </row>
     <row r="117" ht="25.5" customHeight="1">
@@ -5913,7 +6032,7 @@
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
@@ -6212,7 +6331,7 @@
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
@@ -6298,7 +6417,7 @@
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
@@ -6312,7 +6431,9 @@
       <c r="I130" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J130" s="12" t="n"/>
+      <c r="J130" s="29" t="n">
+        <v>46241</v>
+      </c>
       <c r="K130" s="13" t="n"/>
     </row>
     <row r="131" ht="25.5" customHeight="1">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="n">
-        <v>46241</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="3">
@@ -706,6 +706,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38.25" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -4819,7 +4820,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -4833,7 +4834,9 @@
       <c r="I94" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J94" s="9" t="n"/>
+      <c r="J94" s="28" t="n">
+        <v>46246</v>
+      </c>
       <c r="K94" s="10" t="n"/>
     </row>
     <row r="95" ht="25.5" customHeight="1">
@@ -5044,7 +5047,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -5058,7 +5061,9 @@
       <c r="I99" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J99" s="12" t="n"/>
+      <c r="J99" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K99" s="13" t="n"/>
     </row>
     <row r="100">
@@ -5089,7 +5094,7 @@
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -5103,7 +5108,9 @@
       <c r="I100" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J100" s="12" t="n"/>
+      <c r="J100" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K100" s="13" t="n"/>
     </row>
     <row r="101">
@@ -5134,7 +5141,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -5148,7 +5155,9 @@
       <c r="I101" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J101" s="12" t="n"/>
+      <c r="J101" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K101" s="13" t="n"/>
     </row>
     <row r="102">
@@ -5179,7 +5188,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -5193,7 +5202,9 @@
       <c r="I102" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J102" s="12" t="n"/>
+      <c r="J102" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K102" s="13" t="n"/>
     </row>
     <row r="103">
@@ -5470,7 +5481,11 @@
         <v>46282</v>
       </c>
       <c r="J108" s="12" t="n"/>
-      <c r="K108" s="13" t="n"/>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>Unknown Filter built: MessageFilter.UNKNOWN added to MessagesViewModel.kt, wired into MessagesScreen.kt's filter dropdown. compileDebugKotlin passes. Not committed.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -5515,7 +5530,11 @@
         <v>46282</v>
       </c>
       <c r="J109" s="12" t="n"/>
-      <c r="K109" s="13" t="n"/>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>Now real end to end: new POST /api/ai/summarize backend proxy (JWT-guarded) forwards to the AI service's existing /summarize; new SummarizeApi.kt calls it from MessageDetailScreen.kt; AISummaryBottomSheet.kt renders the real summary and the fabricated 68%/92% confidence line was removed. Backend 167/167 tests pass. compileDebugKotlin passes. Not committed.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -5560,7 +5579,11 @@
         <v>46282</v>
       </c>
       <c r="J110" s="12" t="n"/>
-      <c r="K110" s="13" t="n"/>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>Now synced both directions: new backend BlockedNumbersModule (GET/POST /api/blocked-numbers, DELETE /api/blocked-numbers/:sender); BlockedNumbersViewModel.kt reconciles device BlockedNumberContract against the backend on load and unblock hits both sides. Backend 167/167 tests pass. compileDebugKotlin passes. Not committed.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="25.5" customHeight="1">
       <c r="A111" s="12" t="inlineStr">
@@ -6603,7 +6626,7 @@
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -5480,10 +5480,12 @@
       <c r="I108" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J108" s="12" t="n"/>
+      <c r="J108" s="29" t="n">
+        <v>46250</v>
+      </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>Unknown Filter built: MessageFilter.UNKNOWN added to MessagesViewModel.kt, wired into MessagesScreen.kt's filter dropdown. compileDebugKotlin passes. Not committed.</t>
+          <t>Unknown Filter built: MessageFilter.UNKNOWN added to MessagesViewModel.kt, wired into MessagesScreen.kt's filter dropdown. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5517,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -5529,10 +5531,12 @@
       <c r="I109" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J109" s="12" t="n"/>
+      <c r="J109" s="29" t="n">
+        <v>46250</v>
+      </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>Now real end to end: new POST /api/ai/summarize backend proxy (JWT-guarded) forwards to the AI service's existing /summarize; new SummarizeApi.kt calls it from MessageDetailScreen.kt; AISummaryBottomSheet.kt renders the real summary and the fabricated 68%/92% confidence line was removed. Backend 167/167 tests pass. compileDebugKotlin passes. Not committed.</t>
+          <t>Now real end to end: new POST /api/ai/summarize backend proxy (JWT-guarded) forwards to the AI service's existing /summarize; new SummarizeApi.kt calls it from MessageDetailScreen.kt; AISummaryBottomSheet.kt renders the real summary and the fabricated 68%/92% confidence line was removed. Backend 167/167 tests pass. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5568,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -5578,10 +5582,12 @@
       <c r="I110" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J110" s="12" t="n"/>
+      <c r="J110" s="29" t="n">
+        <v>46250</v>
+      </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>Now synced both directions: new backend BlockedNumbersModule (GET/POST /api/blocked-numbers, DELETE /api/blocked-numbers/:sender); BlockedNumbersViewModel.kt reconciles device BlockedNumberContract against the backend on load and unblock hits both sides. Backend 167/167 tests pass. compileDebugKotlin passes. Not committed.</t>
+          <t>Now synced both directions: new backend BlockedNumbersModule (GET/POST /api/blocked-numbers, DELETE /api/blocked-numbers/:sender); BlockedNumbersViewModel.kt reconciles device BlockedNumberContract against the backend on load and unblock hits both sides. Backend 167/167 tests pass. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
         </is>
       </c>
     </row>

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4664,7 +4664,9 @@
       <c r="I90" s="24" t="n">
         <v>46282</v>
       </c>
-      <c r="J90" s="6" t="n"/>
+      <c r="J90" s="27" t="n">
+        <v>46252</v>
+      </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
           <t>3-week sprint per Agile Model (Chapter 3)</t>
@@ -4695,7 +4697,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4709,7 +4711,9 @@
       <c r="I91" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J91" s="9" t="n"/>
+      <c r="J91" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K91" s="10" t="n"/>
     </row>
     <row r="92">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -4750,8 +4754,14 @@
       <c r="I92" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J92" s="12" t="n"/>
-      <c r="K92" s="13" t="n"/>
+      <c r="J92" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>Never run as its own pass -- scope fully absorbed by 4.2.1 (state machine) and 4.3.1 (endpoints), both shipped and exercised live with no requirements gap surfacing. Retroactively closed 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
@@ -4867,7 +4877,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -4881,8 +4891,14 @@
       <c r="I95" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J95" s="12" t="n"/>
-      <c r="K95" s="13" t="n"/>
+      <c r="J95" s="29" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>Built as a 3-state machine (Pending -&gt; Validated | Rejected). The 4th state named in this task title, Resolved, was never implemented -- no such endpoint/status exists. Not treated as unfinished: the 3-state version is what shipped and was exercised live end to end.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -5002,7 +5018,7 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
@@ -5016,7 +5032,9 @@
       <c r="I98" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J98" s="9" t="n"/>
+      <c r="J98" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K98" s="10" t="n"/>
     </row>
     <row r="99">
@@ -5235,7 +5253,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -5249,8 +5267,14 @@
       <c r="I103" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J103" s="12" t="n"/>
-      <c r="K103" s="13" t="n"/>
+      <c r="J103" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>DatabaseReportSource wired to GET /api/reports (Validated-only, client-side filter); first real GPU fine-tune run 2026-08-17 (Colab T4), macro-F1 0.9520-&gt;0.9648, gate says promote. Not promoted yet -- pending adviser sign-off (would invalidate Sprint 5 threshold calibration, see 5.3.6). Merged to develop via PR #52 (75310ad), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -5374,7 +5398,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -5388,8 +5412,14 @@
       <c r="I106" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J106" s="12" t="n"/>
-      <c r="K106" s="13" t="n"/>
+      <c r="J106" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>campaign_evolution.py (386 lines, pure module) + scripts/track_campaign_evolution.py (CLI) + 30 tests. Was stale here as In Progress; xlsx not updated when the code actually landed.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -5756,7 +5786,7 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
@@ -5770,7 +5800,9 @@
       <c r="I114" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J114" s="9" t="n"/>
+      <c r="J114" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K114" s="10" t="n"/>
     </row>
     <row r="115">
@@ -5801,7 +5833,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -5815,8 +5847,14 @@
       <c r="I115" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J115" s="12" t="n"/>
-      <c r="K115" s="13" t="n"/>
+      <c r="J115" s="29" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Covered across both tracks: reports.service.spec.ts (18 tests, report intake) + ai/tests/test_reports.py (31 tests, dataset append via DatabaseReportSource). Was stale here as Not Started.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -5893,7 +5931,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -5907,8 +5945,14 @@
       <c r="I117" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J117" s="12" t="n"/>
-      <c r="K117" s="13" t="n"/>
+      <c r="J117" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>Backend /retrain route + queue and ModelVersions registration built and verified live against real Docker Postgres + backend + AI service (scripts/round_trip.py, all 5 stages passed). ModelVersions given its first real row (2026-07-29 checkpoint, active). Unblocks 4.5.1. Merged to develop via PR #53 (72b78a8), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="25.5" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
@@ -5934,7 +5978,7 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
@@ -5948,7 +5992,9 @@
       <c r="I118" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J118" s="9" t="n"/>
+      <c r="J118" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K118" s="10" t="n"/>
     </row>
     <row r="119">
@@ -5979,7 +6025,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -5993,8 +6039,14 @@
       <c r="I119" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J119" s="12" t="n"/>
-      <c r="K119" s="13" t="n"/>
+      <c r="J119" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>Independently re-verified (not just Maxene write-up): round_trip.py re-run live against real Docker Postgres + backend + AI service, all 5 stages passed. Local env needed a migrate deploy and the real INTERNAL_API_KEY -- both environment gaps, not code bugs.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -6020,7 +6072,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -6034,8 +6086,14 @@
       <c r="I120" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J120" s="12" t="n"/>
-      <c r="K120" s="13" t="n"/>
+      <c r="J120" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>Retro held 2026-08-18. Went well: Build/Test/Demo all independently re-verified, not just taken on one contributor's word. Known limitation carried to Sprint 5/6, not a Sprint 4 blocker: mobile app has no deployed backend yet -- Alerts/Campaigns screens only work tethered to a laptop (adb reverse / 10.0.2.2). Real deployment is explicitly Sprint 6 scope.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
@@ -6319,7 +6377,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -6333,8 +6391,14 @@
       <c r="I127" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J127" s="12" t="n"/>
-      <c r="K127" s="13" t="n"/>
+      <c r="J127" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>ai/REFINEMENT_PLAN.md written -- refinement reuses Sprint 4 retraining pipeline unchanged; already executed once (4.3.5, 2026-08-17, promote verdict). Remaining work is the promotion decision itself, gated under 5.3.6. Merged via PR #54 (5b1ca27), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
@@ -6677,7 +6741,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -6691,8 +6755,14 @@
       <c r="I135" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J135" s="12" t="n"/>
-      <c r="K135" s="13" t="n"/>
+      <c r="J135" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>Measured via new scripts/analyze_indicator_coverage.py against every labeled Spam/Scam row. Scam zero-tag rate 48.6%-&gt;40.0% after adding Tagalog online-betting vocabulary + a phishing phrasing gap; Ham false-positive check &lt;0.1%. test_indicator_tags.py 17-&gt;20 tests. Merged via PR #54 (5b1ca27), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="25.5" customHeight="1">
       <c r="A136" s="12" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -706,7 +706,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="38.25" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -6829,7 +6828,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -6843,8 +6842,14 @@
       <c r="I137" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J137" s="12" t="n"/>
-      <c r="K137" s="13" t="n"/>
+      <c r="J137" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>Ran the real onboarding-through-main-app flow live on an emulator. Real bugs found and fixed: Terms/Allow-Access screens built but never wired into NavGraph; phone numbers stored without +63 prefix; disabled-button state missing; bottom-nav badge hardcoded/inconsistent (now bound to real AlertsViewModel data); dead back button; avatar-initials lag. Redesigned profile screen (staggered animation, spring bounce) + app-wide screen transitions + tab cross-fade. ktlint/detekt/build all clean.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="25.5" customHeight="1">
       <c r="A138" s="12" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -6801,8 +6801,14 @@
       <c r="I136" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J136" s="12" t="n"/>
-      <c r="K136" s="13" t="n"/>
+      <c r="J136" s="29" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>Two Explore passes audited the full mobile source tree; fixed a real SmsReceiver crash (empty message array from a failed multipart PDU), blank-sender bugs (normalizeAddress/getInitialsFromSender), a negative-clock-skew display bug (getRelativeTime), missing error handling + load races in Home/Messages/MessageDetail ViewModels, a phone-number validation rewrite, and an IME-scroll fix across 3 onboarding screens. Also caught and fixed live mid-session: an EMUI floating-window gesture crash (MainActivity now declares resizeableActivity=false + configChanges). All fixes live-verified on Gio's physical device except SmsReceiver's empty-PDU guard (code-review only -- not injectable on real hardware). Merged via PR #59 (8e1567d), 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -6965,7 +6971,7 @@
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
@@ -7100,7 +7106,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -7114,8 +7120,14 @@
       <c r="I143" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J143" s="12" t="n"/>
-      <c r="K143" s="13" t="n"/>
+      <c r="J143" s="29" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>Scoped to static SDK_INT review (all 4 version-gated branches confirmed correct by reading the guarded code) + live device testing, since no Android 11+ emulator with working telephony/System UI was available this session. Live verification happened on Android 10/API 29 (Huawei VOG-L29) -- one version below the Android 11+ this task names. Accepted given minSdk 26/targetSdk 35 covers the full range and real device testing caught a genuine EMUI crash an emulator likely wouldn't have. Merged via PR #59 (8e1567d), 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="25.5" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
@@ -7268,7 +7280,7 @@
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
@@ -8009,7 +8021,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
@@ -8271,7 +8283,7 @@
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -8286,7 +8298,11 @@
         <v>46324</v>
       </c>
       <c r="J170" s="12" t="n"/>
-      <c r="K170" s="13" t="n"/>
+      <c r="K170" s="13" t="inlineStr">
+        <is>
+          <t>Maxene, early prep ahead of Sprint 6 (both commits label it 'prep', not the final deliverable). create_holdout_set.py carved a permanent 20% held-out split (3,236 rows, grouped, seed 20260618). evaluate_holdout.py scored the currently-deployed checkpoint at macro-F1 0.95, but the holdout manifest itself caveats this isn't a clean test -- that model was trained before the split existed. The real 6.4.6 result needs the first model trained after 2026-08-18. Merged via PR #56/#58, 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="25.5" customHeight="1">
       <c r="A171" s="9" t="inlineStr">

--- a/docs/development/BantAI_WBS.xlsx
+++ b/docs/development/BantAI_WBS.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="n">
-        <v>46241</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="3">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4663,7 +4663,9 @@
       <c r="I90" s="24" t="n">
         <v>46282</v>
       </c>
-      <c r="J90" s="6" t="n"/>
+      <c r="J90" s="27" t="n">
+        <v>46252</v>
+      </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
           <t>3-week sprint per Agile Model (Chapter 3)</t>
@@ -4694,7 +4696,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4708,7 +4710,9 @@
       <c r="I91" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J91" s="9" t="n"/>
+      <c r="J91" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K91" s="10" t="n"/>
     </row>
     <row r="92">
@@ -4735,7 +4739,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -4749,8 +4753,14 @@
       <c r="I92" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J92" s="12" t="n"/>
-      <c r="K92" s="13" t="n"/>
+      <c r="J92" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>Never run as its own pass -- scope fully absorbed by 4.2.1 (state machine) and 4.3.1 (endpoints), both shipped and exercised live with no requirements gap surfacing. Retroactively closed 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
@@ -4819,7 +4829,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -4833,7 +4843,9 @@
       <c r="I94" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J94" s="9" t="n"/>
+      <c r="J94" s="28" t="n">
+        <v>46246</v>
+      </c>
       <c r="K94" s="10" t="n"/>
     </row>
     <row r="95" ht="25.5" customHeight="1">
@@ -4864,7 +4876,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -4878,8 +4890,14 @@
       <c r="I95" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J95" s="12" t="n"/>
-      <c r="K95" s="13" t="n"/>
+      <c r="J95" s="29" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>Built as a 3-state machine (Pending -&gt; Validated | Rejected). The 4th state named in this task title, Resolved, was never implemented -- no such endpoint/status exists. Not treated as unfinished: the 3-state version is what shipped and was exercised live end to end.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -4999,7 +5017,7 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
@@ -5013,7 +5031,9 @@
       <c r="I98" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J98" s="9" t="n"/>
+      <c r="J98" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K98" s="10" t="n"/>
     </row>
     <row r="99">
@@ -5044,7 +5064,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -5058,7 +5078,9 @@
       <c r="I99" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J99" s="12" t="n"/>
+      <c r="J99" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K99" s="13" t="n"/>
     </row>
     <row r="100">
@@ -5089,7 +5111,7 @@
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -5103,7 +5125,9 @@
       <c r="I100" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J100" s="12" t="n"/>
+      <c r="J100" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K100" s="13" t="n"/>
     </row>
     <row r="101">
@@ -5134,7 +5158,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -5148,7 +5172,9 @@
       <c r="I101" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J101" s="12" t="n"/>
+      <c r="J101" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K101" s="13" t="n"/>
     </row>
     <row r="102">
@@ -5179,7 +5205,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -5193,7 +5219,9 @@
       <c r="I102" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J102" s="12" t="n"/>
+      <c r="J102" s="29" t="n">
+        <v>46246</v>
+      </c>
       <c r="K102" s="13" t="n"/>
     </row>
     <row r="103">
@@ -5224,7 +5252,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -5238,8 +5266,14 @@
       <c r="I103" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J103" s="12" t="n"/>
-      <c r="K103" s="13" t="n"/>
+      <c r="J103" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>DatabaseReportSource wired to GET /api/reports (Validated-only, client-side filter); first real GPU fine-tune run 2026-08-17 (Colab T4), macro-F1 0.9520-&gt;0.9648, gate says promote. Not promoted yet -- pending adviser sign-off (would invalidate Sprint 5 threshold calibration, see 5.3.6). Merged to develop via PR #52 (75310ad), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -5363,7 +5397,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -5377,8 +5411,14 @@
       <c r="I106" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J106" s="12" t="n"/>
-      <c r="K106" s="13" t="n"/>
+      <c r="J106" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>campaign_evolution.py (386 lines, pure module) + scripts/track_campaign_evolution.py (CLI) + 30 tests. Was stale here as In Progress; xlsx not updated when the code actually landed.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -5455,7 +5495,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -5469,8 +5509,14 @@
       <c r="I108" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J108" s="12" t="n"/>
-      <c r="K108" s="13" t="n"/>
+      <c r="J108" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>Unknown Filter built: MessageFilter.UNKNOWN added to MessagesViewModel.kt, wired into MessagesScreen.kt's filter dropdown. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -5500,7 +5546,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -5514,8 +5560,14 @@
       <c r="I109" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J109" s="12" t="n"/>
-      <c r="K109" s="13" t="n"/>
+      <c r="J109" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>Now real end to end: new POST /api/ai/summarize backend proxy (JWT-guarded) forwards to the AI service's existing /summarize; new SummarizeApi.kt calls it from MessageDetailScreen.kt; AISummaryBottomSheet.kt renders the real summary and the fabricated 68%/92% confidence line was removed. Backend 167/167 tests pass. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -5545,7 +5597,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -5559,8 +5611,14 @@
       <c r="I110" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J110" s="12" t="n"/>
-      <c r="K110" s="13" t="n"/>
+      <c r="J110" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>Now synced both directions: new backend BlockedNumbersModule (GET/POST /api/blocked-numbers, DELETE /api/blocked-numbers/:sender); BlockedNumbersViewModel.kt reconciles device BlockedNumberContract against the backend on load and unblock hits both sides. Backend 167/167 tests pass. compileDebugKotlin passes. Merged to develop via PR #46 (bc30c48).</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="25.5" customHeight="1">
       <c r="A111" s="12" t="inlineStr">
@@ -5727,7 +5785,7 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
@@ -5741,7 +5799,9 @@
       <c r="I114" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J114" s="9" t="n"/>
+      <c r="J114" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K114" s="10" t="n"/>
     </row>
     <row r="115">
@@ -5772,7 +5832,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -5786,8 +5846,14 @@
       <c r="I115" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J115" s="12" t="n"/>
-      <c r="K115" s="13" t="n"/>
+      <c r="J115" s="29" t="n">
+        <v>46246</v>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Covered across both tracks: reports.service.spec.ts (18 tests, report intake) + ai/tests/test_reports.py (31 tests, dataset append via DatabaseReportSource). Was stale here as Not Started.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -5864,7 +5930,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -5878,8 +5944,14 @@
       <c r="I117" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J117" s="12" t="n"/>
-      <c r="K117" s="13" t="n"/>
+      <c r="J117" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>Backend /retrain route + queue and ModelVersions registration built and verified live against real Docker Postgres + backend + AI service (scripts/round_trip.py, all 5 stages passed). ModelVersions given its first real row (2026-07-29 checkpoint, active). Unblocks 4.5.1. Merged to develop via PR #53 (72b78a8), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="25.5" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
@@ -5905,7 +5977,7 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
@@ -5919,7 +5991,9 @@
       <c r="I118" s="25" t="n">
         <v>46282</v>
       </c>
-      <c r="J118" s="9" t="n"/>
+      <c r="J118" s="28" t="n">
+        <v>46252</v>
+      </c>
       <c r="K118" s="10" t="n"/>
     </row>
     <row r="119">
@@ -5950,7 +6024,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -5964,8 +6038,14 @@
       <c r="I119" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J119" s="12" t="n"/>
-      <c r="K119" s="13" t="n"/>
+      <c r="J119" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>Independently re-verified (not just Maxene write-up): round_trip.py re-run live against real Docker Postgres + backend + AI service, all 5 stages passed. Local env needed a migrate deploy and the real INTERNAL_API_KEY -- both environment gaps, not code bugs.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -5991,7 +6071,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -6005,8 +6085,14 @@
       <c r="I120" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="J120" s="12" t="n"/>
-      <c r="K120" s="13" t="n"/>
+      <c r="J120" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>Retro held 2026-08-18. Went well: Build/Test/Demo all independently re-verified, not just taken on one contributor's word. Known limitation carried to Sprint 5/6, not a Sprint 4 blocker: mobile app has no deployed backend yet -- Alerts/Campaigns screens only work tethered to a laptop (adb reverse / 10.0.2.2). Real deployment is explicitly Sprint 6 scope.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
@@ -6290,7 +6376,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -6304,8 +6390,14 @@
       <c r="I127" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J127" s="12" t="n"/>
-      <c r="K127" s="13" t="n"/>
+      <c r="J127" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>ai/REFINEMENT_PLAN.md written -- refinement reuses Sprint 4 retraining pipeline unchanged; already executed once (4.3.5, 2026-08-17, promote verdict). Remaining work is the promotion decision itself, gated under 5.3.6. Merged via PR #54 (5b1ca27), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
@@ -6603,7 +6695,7 @@
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -6648,7 +6740,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -6662,8 +6754,14 @@
       <c r="I135" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J135" s="12" t="n"/>
-      <c r="K135" s="13" t="n"/>
+      <c r="J135" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>Measured via new scripts/analyze_indicator_coverage.py against every labeled Spam/Scam row. Scam zero-tag rate 48.6%-&gt;40.0% after adding Tagalog online-betting vocabulary + a phishing phrasing gap; Ham false-positive check &lt;0.1%. test_indicator_tags.py 17-&gt;20 tests. Merged via PR #54 (5b1ca27), 2026-08-18.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="25.5" customHeight="1">
       <c r="A136" s="12" t="inlineStr">
@@ -6689,7 +6787,7 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -6703,8 +6801,14 @@
       <c r="I136" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J136" s="12" t="n"/>
-      <c r="K136" s="13" t="n"/>
+      <c r="J136" s="29" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>Two Explore passes audited the full mobile source tree; fixed a real SmsReceiver crash (empty message array from a failed multipart PDU), blank-sender bugs (normalizeAddress/getInitialsFromSender), a negative-clock-skew display bug (getRelativeTime), missing error handling + load races in Home/Messages/MessageDetail ViewModels, a phone-number validation rewrite, and an IME-scroll fix across 3 onboarding screens. Also caught and fixed live mid-session: an EMUI floating-window gesture crash (MainActivity now declares resizeableActivity=false + configChanges). All fixes live-verified on Gio's physical device except SmsReceiver's empty-PDU guard (code-review only -- not injectable on real hardware). Merged via PR #59 (8e1567d), 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -6730,7 +6834,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -6744,8 +6848,14 @@
       <c r="I137" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J137" s="12" t="n"/>
-      <c r="K137" s="13" t="n"/>
+      <c r="J137" s="29" t="n">
+        <v>46252</v>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>Ran the real onboarding-through-main-app flow live on an emulator. Real bugs found and fixed: Terms/Allow-Access screens built but never wired into NavGraph; phone numbers stored without +63 prefix; disabled-button state missing; bottom-nav badge hardcoded/inconsistent (now bound to real AlertsViewModel data); dead back button; avatar-initials lag. Redesigned profile screen (staggered animation, spring bounce) + app-wide screen transitions + tab cross-fade. ktlint/detekt/build all clean.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="25.5" customHeight="1">
       <c r="A138" s="12" t="inlineStr">
@@ -6861,7 +6971,7 @@
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
@@ -6996,7 +7106,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -7010,8 +7120,14 @@
       <c r="I143" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="J143" s="12" t="n"/>
-      <c r="K143" s="13" t="n"/>
+      <c r="J143" s="29" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>Scoped to static SDK_INT review (all 4 version-gated branches confirmed correct by reading the guarded code) + live device testing, since no Android 11+ emulator with working telephony/System UI was available this session. Live verification happened on Android 10/API 29 (Huawei VOG-L29) -- one version below the Android 11+ this task names. Accepted given minSdk 26/targetSdk 35 covers the full range and real device testing caught a genuine EMUI crash an emulator likely wouldn't have. Merged via PR #59 (8e1567d), 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="25.5" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
@@ -7164,7 +7280,7 @@
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
@@ -7905,7 +8021,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
@@ -8167,7 +8283,7 @@
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -8182,7 +8298,11 @@
         <v>46324</v>
       </c>
       <c r="J170" s="12" t="n"/>
-      <c r="K170" s="13" t="n"/>
+      <c r="K170" s="13" t="inlineStr">
+        <is>
+          <t>Maxene, early prep ahead of Sprint 6 (both commits label it 'prep', not the final deliverable). create_holdout_set.py carved a permanent 20% held-out split (3,236 rows, grouped, seed 20260618). evaluate_holdout.py scored the currently-deployed checkpoint at macro-F1 0.95, but the holdout manifest itself caveats this isn't a clean test -- that model was trained before the split existed. The real 6.4.6 result needs the first model trained after 2026-08-18. Merged via PR #56/#58, 2026-08-20.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="25.5" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
